--- a/site/StructureDefinition-KBV-PR-WEST-Organization.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T11:00:33+01:00</t>
+    <t>2026-03-18T11:15:18+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1860,7 +1860,7 @@
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="https://fhir.kbv.de/CodeSystem/KBV-CS-WEST-BDT-Betriebsstaettenstatus"/&gt;
+  &lt;system value="https://fhir.kbv.de/CodeSystem/KBV_CS_WEST_BDT_Betriebsstaettenstatus"/&gt;
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
@@ -1876,7 +1876,7 @@
     <t>Organization.type.coding:Betriebsstaettenstatus.system</t>
   </si>
   <si>
-    <t>https://fhir.kbv.de/CodeSystem/KBV-CS-WEST-BDT-Betriebsstaettenstatus</t>
+    <t>https://fhir.kbv.de/CodeSystem/KBV_CS_WEST_BDT_Betriebsstaettenstatus</t>
   </si>
   <si>
     <t>Organization.type.coding:Betriebsstaettenstatus.version</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Organization.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:15:18+01:00</t>
+    <t>2026-03-18T11:53:44+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Organization.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:53:44+01:00</t>
+    <t>2026-03-18T11:15:18+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Organization.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:15:18+01:00</t>
+    <t>2026-03-18T12:55:48+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Organization.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T12:55:48+01:00</t>
+    <t>2026-03-18T17:09:19+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Organization.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-29T11:10:04+02:00</t>
+    <t>2026-06-24T16:51:19+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1871,7 +1871,7 @@
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="https://fhir.kbv.de/CodeSystem/KBV-CS-WEST-BDT-Betriebsstaettenstatus"/&gt;
+  &lt;system value="https://fhir.kbv.de/CodeSystem/KBV_CS_WEST_BDT_Betriebsstaettenstatus"/&gt;
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
@@ -1887,7 +1887,7 @@
     <t>Organization.type.coding:Betriebsstaettenstatus.system</t>
   </si>
   <si>
-    <t>https://fhir.kbv.de/CodeSystem/KBV-CS-WEST-BDT-Betriebsstaettenstatus</t>
+    <t>https://fhir.kbv.de/CodeSystem/KBV_CS_WEST_BDT_Betriebsstaettenstatus</t>
   </si>
   <si>
     <t>Organization.type.coding:Betriebsstaettenstatus.version</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Organization.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:51:19+02:00</t>
+    <t>2026-06-26T18:38:01+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Organization.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T18:38:01+02:00</t>
+    <t>2026-07-06T17:54:18+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Organization.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T17:54:18+02:00</t>
+    <t>2026-07-22T15:49:40+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Organization.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T15:49:40+02:00</t>
+    <t>2026-07-22T16:29:56+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
